--- a/www/download/IND.gross_output.s.mv.rpO1.xlsx
+++ b/www/download/IND.gross_output.s.mv.rpO1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14110760.302</t>
+          <t>14110760302363.2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13858276.656</t>
+          <t>13858276655519.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14322476.615</t>
+          <t>14322476614930.3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14332920.528</t>
+          <t>14332920528044.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>16386349.687</t>
+          <t>16386349687039.1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17849571.218</t>
+          <t>17849571217950.1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17667677.582</t>
+          <t>17667677581600.9</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19331426.451</t>
+          <t>19331426451310.9</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23146999.761</t>
+          <t>23146999761006.9</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24046743.259</t>
+          <t>24046743258964.5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>24002647.414</t>
+          <t>24002647414175.5</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>22228375.421</t>
+          <t>22228375421085.1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>20050217.624</t>
+          <t>20050217623909.3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>16649031.267</t>
+          <t>16649031266656.7</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>15885864.304</t>
+          <t>15885864304010.2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11358921.468</t>
+          <t>11358921467812.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9902551.878</t>
+          <t>9902551878467.27</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9193773.489</t>
+          <t>9193773489484.58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>10452005.637</t>
+          <t>10452005637462.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>11068492.11</t>
+          <t>11068492109541.9</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11425357.592</t>
+          <t>11425357592051.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>12247395.011</t>
+          <t>12247395010550.2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12547991.834</t>
+          <t>12547991834073.8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>14639830.55</t>
+          <t>14639830549625.4</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13759707.891</t>
+          <t>13759707891477.1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>12699533.082</t>
+          <t>12699533082189.2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11737173.649</t>
+          <t>11737173648992.9</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10082988.305</t>
+          <t>10082988304586.6</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>7956110.61</t>
+          <t>7956110610441.12</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>7197990.963</t>
+          <t>7197990963003.93</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12489453.305</t>
+          <t>12489453305017.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10855987.589</t>
+          <t>10855987588717.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10174639.429</t>
+          <t>10174639428610.3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11576236.756</t>
+          <t>11576236755947.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12478523.468</t>
+          <t>12478523467583.9</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13191421.505</t>
+          <t>13191421505443.2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14313714.704</t>
+          <t>14313714703901.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14437237.996</t>
+          <t>14437237995526.3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>16522683.007</t>
+          <t>16522683006911.8</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15756413.087</t>
+          <t>15756413087479.4</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>14304979.545</t>
+          <t>14304979545152.8</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>13276593.795</t>
+          <t>13276593794885.8</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>11396195.296</t>
+          <t>11396195295515.8</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>9544340.846</t>
+          <t>9544340845720.07</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>8570101.32</t>
+          <t>8570101320217.4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>869635.01</t>
+          <t>869635009862.295</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>812017.835</t>
+          <t>812017835239.891</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>670844.701</t>
+          <t>670844701141.402</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>809196.697</t>
+          <t>809196697426.37</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>833794.959</t>
+          <t>833794958988.777</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>877348.451</t>
+          <t>877348451161.209</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>981991.343</t>
+          <t>981991342681.094</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1037024.426</t>
+          <t>1037024426015.48</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1271062.531</t>
+          <t>1271062531427.77</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1306117.231</t>
+          <t>1306117231157.62</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1307972.145</t>
+          <t>1307972144663.32</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1333571.109</t>
+          <t>1333571109351.67</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1309764.886</t>
+          <t>1309764885938.7</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1199800.242</t>
+          <t>1199800241778.63</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1129111.963</t>
+          <t>1129111963470.04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>24179638.904</t>
+          <t>24179638904178</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>23624925.652</t>
+          <t>23624925651529.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24796639.941</t>
+          <t>24796639940830.4</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>26841983.107</t>
+          <t>26841983106506.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19950777.032</t>
+          <t>19950777031738.5</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>26840146.372</t>
+          <t>26840146372245.8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>24851913.448</t>
+          <t>24851913447990.1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22067089.626</t>
+          <t>22067089625869.1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>22855527.345</t>
+          <t>22855527345276.7</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23300759.863</t>
+          <t>23300759862716.2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>27597614.638</t>
+          <t>27597614637785.9</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28484944.601</t>
+          <t>28484944601259.8</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>30747501.717</t>
+          <t>30747501717255.3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>28385658.935</t>
+          <t>28385658934862.6</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>26893736.832</t>
+          <t>26893736832383.7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>22232756.829</t>
+          <t>22232756829429.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20682731.386</t>
+          <t>20682731385931.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22223407.218</t>
+          <t>22223407218255.9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24276963.997</t>
+          <t>24276963997115.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>27838617.883</t>
+          <t>27838617883292.1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>34739029.491</t>
+          <t>34739029490629.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>36509283.125</t>
+          <t>36509283125075.7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>35341331.098</t>
+          <t>35341331097870</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>38920246.876</t>
+          <t>38920246875589.9</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>37034305.129</t>
+          <t>37034305128642.2</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>37215964.712</t>
+          <t>37215964711942.2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>36083003.225</t>
+          <t>36083003224622.9</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>29346599.984</t>
+          <t>29346599983957.5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>23667831.64</t>
+          <t>23667831639976.4</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>20730143.369</t>
+          <t>20730143369101.8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>64560925.153</t>
+          <t>64560925152950.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>68692314.779</t>
+          <t>68692314779276.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78001417.58</t>
+          <t>78001417579692.3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>90616576.245</t>
+          <t>90616576245472.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>101138935.808</t>
+          <t>101138935808091</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>125125976.491</t>
+          <t>125125976490954</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>143864753.195</t>
+          <t>143864753195171</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>147688385.568</t>
+          <t>147688385567641</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>163125241.849</t>
+          <t>163125241849057</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>165005889.157</t>
+          <t>165005889156872</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>174605757.798</t>
+          <t>174605757797661</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>183104855.003</t>
+          <t>183104855003390</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>172773338.103</t>
+          <t>172773338103131</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>166486923.778</t>
+          <t>166486923778059</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>171105462.097</t>
+          <t>171105462096750</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>296762.977</t>
+          <t>296762977290.803</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>274388.098</t>
+          <t>274388097928.136</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>272857.064</t>
+          <t>272857063851.275</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>311345.771</t>
+          <t>311345771067.213</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>338127.426</t>
+          <t>338127425608.22</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>357760.131</t>
+          <t>357760130582.843</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>382982.284</t>
+          <t>382982284108.93</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>414006.174</t>
+          <t>414006174206.577</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>509067.818</t>
+          <t>509067818002.756</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>492024.406</t>
+          <t>492024405734.744</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>469545.228</t>
+          <t>469545228210.605</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>435307.133</t>
+          <t>435307133173.646</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>374741.169</t>
+          <t>374741169410.785</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>336571.962</t>
+          <t>336571962183.328</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>307785.272</t>
+          <t>307785271811.902</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2947205.81</t>
+          <t>2947205809562.53</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>3536211.108</t>
+          <t>3536211108101.91</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3499303.358</t>
+          <t>3499303357961.78</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>4199880.072</t>
+          <t>4199880072401.95</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4299189.659</t>
+          <t>4299189659105.63</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4616914.214</t>
+          <t>4616914214070.52</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5532543.607</t>
+          <t>5532543606566.28</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6380983.164</t>
+          <t>6380983163690.67</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7308931.79</t>
+          <t>7308931789645.27</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>7095976.587</t>
+          <t>7095976586566.76</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7052561.406</t>
+          <t>7052561406257.96</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>7094127.054</t>
+          <t>7094127054444.38</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>6350424.684</t>
+          <t>6350424683580.22</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5298372.25</t>
+          <t>5298372250073.94</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>4045391.26</t>
+          <t>4045391260255.32</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>110061297.068</t>
+          <t>110061297068338</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>94542055.568</t>
+          <t>94542055568472.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>86290083.55</t>
+          <t>86290083549549.5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>97330142.56</t>
+          <t>97330142559753.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>102266186.599</t>
+          <t>102266186599350</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>108555469.994</t>
+          <t>108555469993660</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>114219295.823</t>
+          <t>114219295822503</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>114796339.378</t>
+          <t>114796339378179</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>130273893.593</t>
+          <t>130273893592652</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>121176941.641</t>
+          <t>121176941640695</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>109281646.868</t>
+          <t>109281646867671</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>98637671.004</t>
+          <t>98637671004184.5</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>83487844.065</t>
+          <t>83487844065090.9</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>64353263.397</t>
+          <t>64353263396668</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>56337439.119</t>
+          <t>56337439118620.1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7094252.15</t>
+          <t>7094252149815.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6415796.253</t>
+          <t>6415796252936.85</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6056708.886</t>
+          <t>6056708886210.7</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7012859.089</t>
+          <t>7012859089007.87</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7468576.702</t>
+          <t>7468576701759.99</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7847415.247</t>
+          <t>7847415246889.66</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8454239.306</t>
+          <t>8454239306450.65</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8728335.918</t>
+          <t>8728335918096.62</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10093055.979</t>
+          <t>10093055979170.2</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9505560.338</t>
+          <t>9505560338035.76</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>8954829.006</t>
+          <t>8954829005555.74</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>8214549.212</t>
+          <t>8214549211991.09</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7083196.371</t>
+          <t>7083196371169.75</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>5637472.225</t>
+          <t>5637472224581.28</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5098763.176</t>
+          <t>5098763176222.58</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>26811704.476</t>
+          <t>26811704476428</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>24951462.627</t>
+          <t>24951462627325.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23970197.68</t>
+          <t>23970197679817.8</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27886695.29</t>
+          <t>27886695290078.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>30748486.547</t>
+          <t>30748486546906.8</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>33466285.922</t>
+          <t>33466285922433.1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>37339209.31</t>
+          <t>37339209309712.9</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>40718161.416</t>
+          <t>40718161415613.2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>49396859.675</t>
+          <t>49396859674894.1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>48148447.845</t>
+          <t>48148447844952.5</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>47083430.874</t>
+          <t>47083430874302.8</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>44524301.73</t>
+          <t>44524301729607.5</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>38585285.497</t>
+          <t>38585285497179.7</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>30289896.4</t>
+          <t>30289896399568.8</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>25762419.393</t>
+          <t>25762419393220.5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>227678.561</t>
+          <t>227678561341.457</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>228631.039</t>
+          <t>228631038974.471</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>248032.104</t>
+          <t>248032104072.309</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>302693.237</t>
+          <t>302693237352.479</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>301055.069</t>
+          <t>301055068696.806</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>365953.803</t>
+          <t>365953802604.266</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>424540.644</t>
+          <t>424540644384.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>454022.989</t>
+          <t>454022989300.046</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>556037.247</t>
+          <t>556037247418.192</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>590295.462</t>
+          <t>590295461531.758</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>596003.003</t>
+          <t>596003002906.574</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>586130.949</t>
+          <t>586130948799.981</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>552649.536</t>
+          <t>552649535849.634</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>485503.9</t>
+          <t>485503900148.904</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>363202.651</t>
+          <t>363202650788.36</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6807103.392</t>
+          <t>6807103392265.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5954015.338</t>
+          <t>5954015337592.46</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5805512.164</t>
+          <t>5805512163617.79</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6675607.106</t>
+          <t>6675607106022.48</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7212899.134</t>
+          <t>7212899134217.6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7757598.606</t>
+          <t>7757598606241.74</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8346560.576</t>
+          <t>8346560576273.53</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8520206.059</t>
+          <t>8520206058527.93</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>9846767.941</t>
+          <t>9846767941282.6</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>9454165.372</t>
+          <t>9454165372174.77</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>8916673.523</t>
+          <t>8916673522832.49</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>8278660.681</t>
+          <t>8278660680606.09</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7131151.429</t>
+          <t>7131151428785.18</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>5691513.021</t>
+          <t>5691513020705.38</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4924339.99</t>
+          <t>4924339989942.08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>57304285.036</t>
+          <t>57304285035683.1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>51313112.643</t>
+          <t>51313112643083.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47689601.055</t>
+          <t>47689601054992.2</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53934098.922</t>
+          <t>53934098922407.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>58923652.557</t>
+          <t>58923652556603</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>62507892.615</t>
+          <t>62507892615338.7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>66997050.651</t>
+          <t>66997050651384.3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>69304364.647</t>
+          <t>69304364647223</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>79962110.333</t>
+          <t>79962110333458.3</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>76102096.339</t>
+          <t>76102096339213.8</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>71094670.784</t>
+          <t>71094670784256.7</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>64271929.716</t>
+          <t>64271929715988.4</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>54919695.189</t>
+          <t>54919695188620.4</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>43012919.555</t>
+          <t>43012919555341.5</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>39043579.174</t>
+          <t>39043579173997</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>48455923.303</t>
+          <t>48455923303399.6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44516533.631</t>
+          <t>44516533631290.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>49932966.381</t>
+          <t>49932966380959.9</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>58809616.512</t>
+          <t>58809616511585.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>64388451.996</t>
+          <t>64388451996073</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>72220728.837</t>
+          <t>72220728836614.2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>75815201.484</t>
+          <t>75815201484467.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78587090.909</t>
+          <t>78587090908691.7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>84998014.145</t>
+          <t>84998014144863.6</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>83849499.26</t>
+          <t>83849499260141.4</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>80644299.121</t>
+          <t>80644299120837.8</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>73519453.578</t>
+          <t>73519453578153.4</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>62835582.739</t>
+          <t>62835582739004</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>42864712.443</t>
+          <t>42864712442778.8</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>35449052.13</t>
+          <t>35449052129856.8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4216599.858</t>
+          <t>4216599858378.96</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4013112.107</t>
+          <t>4013112107277.72</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3955753.096</t>
+          <t>3955753095859.78</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4378575.316</t>
+          <t>4378575315919.98</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4891528.322</t>
+          <t>4891528321704.55</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5180871.418</t>
+          <t>5180871417719.93</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5509487.276</t>
+          <t>5509487276197.81</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6387309.877</t>
+          <t>6387309877259.59</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>7803753.085</t>
+          <t>7803753084710.83</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7469560.652</t>
+          <t>7469560651674.54</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7072537.748</t>
+          <t>7072537748473.38</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>6706371.162</t>
+          <t>6706371162027.14</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5768017.58</t>
+          <t>5768017580094.82</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4815052.35</t>
+          <t>4815052349980.27</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4342030.611</t>
+          <t>4342030611101.21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2778749.986</t>
+          <t>2778749986139.68</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2458663.898</t>
+          <t>2458663897956.22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2574704.106</t>
+          <t>2574704105514.69</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2917386.068</t>
+          <t>2917386067559.87</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3193301.745</t>
+          <t>3193301745050.09</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3681081.128</t>
+          <t>3681081128453.42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4143364.003</t>
+          <t>4143364003437.79</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4630949.826</t>
+          <t>4630949826326.04</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5392239.48</t>
+          <t>5392239479830.84</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5331722.704</t>
+          <t>5331722703574.77</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5164430.122</t>
+          <t>5164430121970.11</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4547536.921</t>
+          <t>4547536920938.16</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4008345.454</t>
+          <t>4008345454260.29</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3032180.262</t>
+          <t>3032180261923.04</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2269275.883</t>
+          <t>2269275882668.18</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10751340.721</t>
+          <t>10751340721117.5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11616444.882</t>
+          <t>11616444882099.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>12500885.378</t>
+          <t>12500885378295.2</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>5511362.868</t>
+          <t>5511362867679.95</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9034716.304</t>
+          <t>9034716304449.71</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>10907868.469</t>
+          <t>10907868468971.8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10725087.255</t>
+          <t>10725087255240.5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>12236905.167</t>
+          <t>12236905166631.3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>13378459.076</t>
+          <t>13378459075714.9</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11600128.512</t>
+          <t>11600128511871.1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10560077.309</t>
+          <t>10560077309330.8</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>12143833.824</t>
+          <t>12143833823739.9</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>10662982.462</t>
+          <t>10662982462168.7</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>9974238.847</t>
+          <t>9974238847280.03</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10247287.385</t>
+          <t>10247287385230.8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21060393.821</t>
+          <t>21060393820932</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18461154.757</t>
+          <t>18461154757292.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>21577848.998</t>
+          <t>21577848998470.2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23158879.071</t>
+          <t>23158879071099.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>25758638.209</t>
+          <t>25758638208581.9</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>31344476.702</t>
+          <t>31344476702479.4</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>34480908.635</t>
+          <t>34480908635137.6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>34324299.598</t>
+          <t>34324299597503.5</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>37838084.853</t>
+          <t>37838084853173</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>36902290.952</t>
+          <t>36902290952068.2</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38636461.288</t>
+          <t>38636461287942.2</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>38460722.6</t>
+          <t>38460722599823.1</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>36211130.121</t>
+          <t>36211130121369.6</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>29334324.51</t>
+          <t>29334324510395.1</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>28946235.119</t>
+          <t>28946235118618.6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3528436.542</t>
+          <t>3528436542039.88</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3351280.261</t>
+          <t>3351280260829.56</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3612105.641</t>
+          <t>3612105640973.95</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4143528.769</t>
+          <t>4143528768572.03</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4794617.919</t>
+          <t>4794617918836.36</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5551519.036</t>
+          <t>5551519036320.75</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6333496.627</t>
+          <t>6333496626944.51</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6437501.626</t>
+          <t>6437501625762.02</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>7821801.35</t>
+          <t>7821801350398.17</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>7792788.321</t>
+          <t>7792788320872.48</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>7723840.355</t>
+          <t>7723840355468.57</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>7428897.419</t>
+          <t>7428897419024.04</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6636307.251</t>
+          <t>6636307251238.65</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5200449.911</t>
+          <t>5200449910583.61</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4468278.984</t>
+          <t>4468278984467.79</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>52459262.596</t>
+          <t>52459262595967.5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51589850.851</t>
+          <t>51589850850875.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>51368112.9</t>
+          <t>51368112899889</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>56563785.696</t>
+          <t>56563785695823</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>59982968.681</t>
+          <t>59982968681488.6</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>62554424.683</t>
+          <t>62554424683383.2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>67216393.558</t>
+          <t>67216393557625.4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>70435511.185</t>
+          <t>70435511184604.1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>82849135.954</t>
+          <t>82849135953604.2</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>78270721.548</t>
+          <t>78270721548012.8</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>72992133.65</t>
+          <t>72992133650355.4</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>66898990.912</t>
+          <t>66898990912323.7</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>57022794.158</t>
+          <t>57022794157828</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>42951239.053</t>
+          <t>42951239052969</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>36365543.647</t>
+          <t>36365543647354.1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>228157289.675</t>
+          <t>228157289675262</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>177859220.42</t>
+          <t>177859220419513</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>169666790.316</t>
+          <t>169666790315899</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>170730243.263</t>
+          <t>170730243262577</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>209864667.018</t>
+          <t>209864667017625</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>256463643.676</t>
+          <t>256463643676375</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>239491916.021</t>
+          <t>239491916021252</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>216067745.31</t>
+          <t>216067745310331</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>220263263.661</t>
+          <t>220263263661182</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>200704093.607</t>
+          <t>200704093607379</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>178985373.46</t>
+          <t>178985373460202</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>150546503.571</t>
+          <t>150546503570772</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>115537879.456</t>
+          <t>115537879455731</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>99534490.753</t>
+          <t>99534490752909.4</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>92474777.619</t>
+          <t>92474777618826.8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>37966219.052</t>
+          <t>37966219051946.4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>37504881.968</t>
+          <t>37504881967624</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35712366.304</t>
+          <t>35712366303826.6</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>27143874.641</t>
+          <t>27143874640954.1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>35178333.384</t>
+          <t>35178333384029</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>46765126.614</t>
+          <t>46765126613740.4</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>47698517.4</t>
+          <t>47698517400474.2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>51074387.566</t>
+          <t>51074387565602.9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>55190632.172</t>
+          <t>55190632172356.5</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>52898856.214</t>
+          <t>52898856213579.4</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>57831830.219</t>
+          <t>57831830219335.9</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>56268820.023</t>
+          <t>56268820023357.6</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>46415659.254</t>
+          <t>46415659253540.6</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>34062035.169</t>
+          <t>34062035168890.8</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>29014081.647</t>
+          <t>29014081646529.5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>321741.857</t>
+          <t>321741856931.449</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>377689.803</t>
+          <t>377689803243.728</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>448863.628</t>
+          <t>448863627859.117</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>546619.075</t>
+          <t>546619075424.632</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>555925.551</t>
+          <t>555925550817.227</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>632337.005</t>
+          <t>632337004942.247</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>732046.041</t>
+          <t>732046040580.895</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>783304.035</t>
+          <t>783304035285.788</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>973786.566</t>
+          <t>973786565517.207</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1016777.556</t>
+          <t>1016777555568.14</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1065428.744</t>
+          <t>1065428744205.98</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1063563.142</t>
+          <t>1063563142252.14</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1006629.068</t>
+          <t>1006629068305.14</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>944656.134</t>
+          <t>944656134218.111</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>697313.717</t>
+          <t>697313717071.564</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>625164.587</t>
+          <t>625164586643.544</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>541635.013</t>
+          <t>541635013232.39</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>515117.229</t>
+          <t>515117228940.736</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>598390.188</t>
+          <t>598390188492.54</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>639556.655</t>
+          <t>639556654598.886</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>691501.993</t>
+          <t>691501992986.307</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>772715.12</t>
+          <t>772715120097.604</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>819927.97</t>
+          <t>819927969518.38</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1003731.569</t>
+          <t>1003731568940.93</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>997169.267</t>
+          <t>997169267257.527</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>936397.319</t>
+          <t>936397319473.924</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>850446.512</t>
+          <t>850446511659.092</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>738775.838</t>
+          <t>738775838016.234</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>653583.706</t>
+          <t>653583705834.993</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>601710.227</t>
+          <t>601710227480.16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>230750.391</t>
+          <t>230750390596.673</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>235204.619</t>
+          <t>235204618866.836</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>283827.95</t>
+          <t>283827950416.235</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>330019.201</t>
+          <t>330019200842.025</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>342388.975</t>
+          <t>342388975063.829</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>386375.695</t>
+          <t>386375695032.718</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>431292.327</t>
+          <t>431292326983.38</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>454620.398</t>
+          <t>454620397525.955</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>547225.919</t>
+          <t>547225919263.863</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>559373.698</t>
+          <t>559373698495.177</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>628488.224</t>
+          <t>628488224103.754</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>702610.763</t>
+          <t>702610762987.766</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>754735.163</t>
+          <t>754735163280.957</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>683071.725</t>
+          <t>683071724649.961</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>433634.985</t>
+          <t>433634985320.837</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>9959243.885</t>
+          <t>9959243884986.26</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10019432.902</t>
+          <t>10019432902038.1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12555135.522</t>
+          <t>12555135522348.9</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15982890.647</t>
+          <t>15982890646639.7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>19894884.383</t>
+          <t>19894884382891.5</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>27501073.859</t>
+          <t>27501073858757.7</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>31810262.684</t>
+          <t>31810262684203.8</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>30656465.161</t>
+          <t>30656465161113.4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>27688264.636</t>
+          <t>27688264635604.5</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>23986908.577</t>
+          <t>23986908576708.4</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>23890248.059</t>
+          <t>23890248059224.3</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>22181999.544</t>
+          <t>22181999544168.5</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>17534124.373</t>
+          <t>17534124372581.8</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>13874418.14</t>
+          <t>13874418139813.3</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>10766957.776</t>
+          <t>10766957775554.5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>169708.955</t>
+          <t>169708954786.404</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>151538.089</t>
+          <t>151538089281.315</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>146904.893</t>
+          <t>146904893423.557</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>180639</t>
+          <t>180638999592.801</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>203995.758</t>
+          <t>203995758474.796</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>243113.737</t>
+          <t>243113737161.229</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>230664.009</t>
+          <t>230664009246.658</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>242732.279</t>
+          <t>242732279254.713</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>271298.21</t>
+          <t>271298210037.93</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>246092.748</t>
+          <t>246092748110.287</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>223009.406</t>
+          <t>223009405788.694</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>208791.287</t>
+          <t>208791286833.404</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>175268.633</t>
+          <t>175268633457.321</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>161881.756</t>
+          <t>161881755668.58</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>133917.565</t>
+          <t>133917565023.159</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>16617183.698</t>
+          <t>16617183697930.3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>14719655.264</t>
+          <t>14719655264060.7</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13858698.508</t>
+          <t>13858698507869.9</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15826145.024</t>
+          <t>15826145023772</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>17199577.861</t>
+          <t>17199577861453.1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>18516347.093</t>
+          <t>18516347092995.6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>20063132.783</t>
+          <t>20063132782962.2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>21003094.633</t>
+          <t>21003094633117.9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>24350821.771</t>
+          <t>24350821770600.7</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>23147563.351</t>
+          <t>23147563351231.2</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>21297388.8</t>
+          <t>21297388799878.2</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>19438913.915</t>
+          <t>19438913914764.6</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>16778922.922</t>
+          <t>16778922922273</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>13914962.517</t>
+          <t>13914962517372.6</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12329680.2</t>
+          <t>12329680199837.9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>13843774.276</t>
+          <t>13843774276424.4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13499873.8</t>
+          <t>13499873800184.2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13827156.846</t>
+          <t>13827156845664.3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>17438089.765</t>
+          <t>17438089765289.9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18464987.414</t>
+          <t>18464987413550.7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>16401693.413</t>
+          <t>16401693412935</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17144240.587</t>
+          <t>17144240586663.2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>15546180.554</t>
+          <t>15546180553684.2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15733593.693</t>
+          <t>15733593692813.6</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>14822289.812</t>
+          <t>14822289811671.3</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15576321.315</t>
+          <t>15576321315040.1</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>14374065.486</t>
+          <t>14374065485543</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>13365066.98</t>
+          <t>13365066979711.1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>11855355.521</t>
+          <t>11855355520668.5</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>8893588.815</t>
+          <t>8893588815403.04</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5250171.085</t>
+          <t>5250171084551.64</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4984116.04</t>
+          <t>4984116040197.72</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4980292.648</t>
+          <t>4980292648344.21</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5780647.014</t>
+          <t>5780647013979.27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6329079.386</t>
+          <t>6329079385786.39</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7006378.679</t>
+          <t>7006378679487.42</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7659909.448</t>
+          <t>7659909448319.14</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>7959849.626</t>
+          <t>7959849625722.16</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>9109720.236</t>
+          <t>9109720236253.04</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>8675019.77</t>
+          <t>8675019770176.88</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>8083304.198</t>
+          <t>8083304197561.45</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7235998.234</t>
+          <t>7235998233915.82</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>6215395.031</t>
+          <t>6215395031040.05</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>5137963.845</t>
+          <t>5137963845118.15</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>4284204.615</t>
+          <t>4284204615360.42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3037516.31</t>
+          <t>3037516309778.51</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2914905.019</t>
+          <t>2914905019156.39</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2497088.343</t>
+          <t>2497088343061.08</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>3569424.958</t>
+          <t>3569424958492.06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2932339.446</t>
+          <t>2932339445592.48</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>3703933.873</t>
+          <t>3703933873055.8</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4921139.432</t>
+          <t>4921139432266</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5347809.959</t>
+          <t>5347809958898.18</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6505968.284</t>
+          <t>6505968283709.87</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5221748.536</t>
+          <t>5221748535632.52</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>6872250.011</t>
+          <t>6872250010992.54</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>7215028.64</t>
+          <t>7215028639963.95</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>6937109.801</t>
+          <t>6937109800747.94</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6542782.755</t>
+          <t>6542782754609.43</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4813354.494</t>
+          <t>4813354493871.49</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>15914866.944</t>
+          <t>15914866943825</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>17668261.74</t>
+          <t>17668261739792.7</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18217992.332</t>
+          <t>18217992331915.2</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>15644084.82</t>
+          <t>15644084819711.7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>9695945.39</t>
+          <t>9695945390017.64</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>14340420.768</t>
+          <t>14340420767620.3</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>18093928.904</t>
+          <t>18093928904329.4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>20477287.292</t>
+          <t>20477287292104.8</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>23725127.699</t>
+          <t>23725127698686.6</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>25497237.498</t>
+          <t>25497237497752.2</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>28764788.343</t>
+          <t>28764788342691.6</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>30982661.862</t>
+          <t>30982661862318.6</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>30237576.766</t>
+          <t>30237576766340</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>28345783.202</t>
+          <t>28345783202227</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>20404609.236</t>
+          <t>20404609236419.9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>911215.38</t>
+          <t>911215379645.226</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>932543.175</t>
+          <t>932543175351.928</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>983114.155</t>
+          <t>983114154590.248</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1165113.471</t>
+          <t>1165113471281.42</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1094013.993</t>
+          <t>1094013992670.9</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1252189.204</t>
+          <t>1252189203773.17</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1437982.125</t>
+          <t>1437982124746.11</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1571416.095</t>
+          <t>1571416095386.42</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2076071.739</t>
+          <t>2076071738970.94</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1999484.058</t>
+          <t>1999484058468.16</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>1989890.213</t>
+          <t>1989890213091.99</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026698.183</t>
+          <t>2026698182552.11</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1962896.753</t>
+          <t>1962896753412.96</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1857453.096</t>
+          <t>1857453096055.45</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1585088.435</t>
+          <t>1585088434958.13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1465292.507</t>
+          <t>1465292506829.35</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1268146.454</t>
+          <t>1268146454065.33</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1226600.674</t>
+          <t>1226600674092.55</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1415090.546</t>
+          <t>1415090546049.26</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1485109.962</t>
+          <t>1485109962450.43</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1574971.89</t>
+          <t>1574971890319</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1703504.69</t>
+          <t>1703504689955.45</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1779481.553</t>
+          <t>1779481553373.65</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2082468.144</t>
+          <t>2082468144021.47</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2024860.959</t>
+          <t>2024860959421.96</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1920924.584</t>
+          <t>1920924584155.76</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1768659.929</t>
+          <t>1768659928617.31</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1586841.745</t>
+          <t>1586841744778.26</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1383663.135</t>
+          <t>1383663134793.18</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1172770.644</t>
+          <t>1172770643576.6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10624423.265</t>
+          <t>10624423264975.6</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10562183.887</t>
+          <t>10562183887490.5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>10063759.221</t>
+          <t>10063759221230.3</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>11289162.205</t>
+          <t>11289162204696.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>12121884.777</t>
+          <t>12121884777132.8</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>13604778.653</t>
+          <t>13604778652915.3</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>13667782.66</t>
+          <t>13667782660149.5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>14283966.206</t>
+          <t>14283966206423.6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>16703557.081</t>
+          <t>16703557080736.3</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>15761279.18</t>
+          <t>15761279179941.1</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>14500735.029</t>
+          <t>14500735028668.3</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>13073568.089</t>
+          <t>13073568089251.5</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>11485981.757</t>
+          <t>11485981756918.4</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>8624631.637</t>
+          <t>8624631636576.87</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>6922657.846</t>
+          <t>6922657845828.98</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>8088444.714</t>
+          <t>8088444714142.26</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8316095.342</t>
+          <t>8316095341620.34</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9608939.034</t>
+          <t>9608939034190.01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>11695257.197</t>
+          <t>11695257197036</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13082443.553</t>
+          <t>13082443552747.4</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>16001421.899</t>
+          <t>16001421898540.3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>12578688.445</t>
+          <t>12578688444782.7</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>13498118.996</t>
+          <t>13498118996433.8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>16386375.515</t>
+          <t>16386375514601.5</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>17353148.693</t>
+          <t>17353148693171.3</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19686747.598</t>
+          <t>19686747598400.8</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>18046590.358</t>
+          <t>18046590357580.4</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>16083694.373</t>
+          <t>16083694372739</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>13165708.602</t>
+          <t>13165708601825</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>10473229.146</t>
+          <t>10473229145836</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>13852353.835</t>
+          <t>13852353835308.4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12300106.832</t>
+          <t>12300106831617.7</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>12718303.549</t>
+          <t>12718303548925.9</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12623913.604</t>
+          <t>12623913603660.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>14708378.212</t>
+          <t>14708378211520</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18558277.824</t>
+          <t>18558277823904</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17255677.868</t>
+          <t>17255677867989.8</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16487089.286</t>
+          <t>16487089285592.3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>16669580.973</t>
+          <t>16669580972995.8</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>16174907.956</t>
+          <t>16174907956075.1</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>15774931.838</t>
+          <t>15774931838478.1</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>14704032.893</t>
+          <t>14704032893487.5</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>11746903.215</t>
+          <t>11746903214799</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>9622679.847</t>
+          <t>9622679846882.36</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7449868.836</t>
+          <t>7449868835633.71</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>233763522.936</t>
+          <t>233763522935616</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>215506472.888</t>
+          <t>215506472887743</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>235602145.538</t>
+          <t>235602145537844</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>278953091.968</t>
+          <t>278953091968497</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>317773814.309</t>
+          <t>317773814309304</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>384868282.359</t>
+          <t>384868282359133</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>411953200.376</t>
+          <t>411953200376317</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>396286449.232</t>
+          <t>396286449232101</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>390356410.094</t>
+          <t>390356410093944</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>342227273.005</t>
+          <t>342227273005380</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>324916921.684</t>
+          <t>324916921684426</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>298451663.617</t>
+          <t>298451663617376</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>234772200.464</t>
+          <t>234772200463920</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>184483790.967</t>
+          <t>184483790966894</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>160319623.563</t>
+          <t>160319623562978</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>122053113.881</t>
+          <t>122053113881417</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>119009606.318</t>
+          <t>119009606317833</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>123258518.941</t>
+          <t>123258518941476</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>126650917.709</t>
+          <t>126650917708868</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>139407474.956</t>
+          <t>139407474955530</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>173909326.334</t>
+          <t>173909326333619</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>182665087.806</t>
+          <t>182665087806477</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>178874710.384</t>
+          <t>178874710383648</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>194866676.208</t>
+          <t>194866676208319</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>192269911.772</t>
+          <t>192269911771926</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>207533588.071</t>
+          <t>207533588071386</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>207661089.271</t>
+          <t>207661089271246</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>181654716.26</t>
+          <t>181654716259591</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>174108114.171</t>
+          <t>174108114170917</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>150156272.506</t>
+          <t>150156272506233</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1227455084.502</t>
+          <t>1227455084501909</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1120023088.41</t>
+          <t>1120023088409631</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1144909486.965</t>
+          <t>1144909486964899</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1249605953.61</t>
+          <t>1249605953610164</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1394272688.796</t>
+          <t>1394272688795963</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>1649386306.493</t>
+          <t>1649386306493491</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1726668778.175</t>
+          <t>1726668778175202</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1708021111.465</t>
+          <t>1708021111465038</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1833014378.406</t>
+          <t>1833014378406269</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>1729576151.812</t>
+          <t>1729576151812375</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>1698456176.737</t>
+          <t>1698456176737048</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>1604798706.017</t>
+          <t>1604798706017060</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>1372327131.471</t>
+          <t>1372327131471129</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>1156124434.079</t>
+          <t>1156124434078601</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>1032410376.515</t>
+          <t>1032410376514836</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
